--- a/jobs13C15N/diet_pos_all_13C15N_tracing.xlsx
+++ b/jobs13C15N/diet_pos_all_13C15N_tracing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\autopeak\jobs13C15N\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxing\Documents\GitHub\autopeak\jobs13C15N\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE86D3D5-AF5F-421F-8817-49A86EB73004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B32768F-5549-43E7-B00D-E3DC1ABF330D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="2355" windowWidth="21600" windowHeight="11295" xr2:uid="{E04B5630-A969-4066-AB24-7618A912BDD5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E04B5630-A969-4066-AB24-7618A912BDD5}"/>
   </bookViews>
   <sheets>
     <sheet name="diet_pos" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="185">
   <si>
     <t>folder</t>
   </si>
@@ -591,6 +591,9 @@
   </si>
   <si>
     <t>pklist_diet_pos_8080</t>
+  </si>
+  <si>
+    <t>mzxml;pos;val-;M27</t>
   </si>
 </sst>
 </file>
@@ -647,11 +650,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1374,7 +1376,7 @@
         <v>183</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1546,7 +1548,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="A40" t="s">
         <v>180</v>
       </c>
       <c r="B40" t="s">
@@ -1563,7 +1565,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
+      <c r="A41" t="s">
         <v>180</v>
       </c>
       <c r="B41" t="s">
@@ -1580,7 +1582,7 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
+      <c r="A42" t="s">
         <v>180</v>
       </c>
       <c r="B42" t="s">
@@ -1597,7 +1599,7 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="A43" t="s">
         <v>180</v>
       </c>
       <c r="B43" t="s">
@@ -1920,7 +1922,7 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+      <c r="A65" t="s">
         <v>181</v>
       </c>
       <c r="B65" t="s">
